--- a/data.mn/public/datasets/temperature-regional.xlsx
+++ b/data.mn/public/datasets/temperature-regional.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6153,6 +6153,28 @@
         <v>19.3</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C261" t="n">
+        <v>22</v>
+      </c>
+      <c r="D261" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E261" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F261" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6164,7 +6186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11903,6 +11925,28 @@
         <v>22.4</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>22</v>
+      </c>
+      <c r="C261" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D261" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E261" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F261" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.mn/public/datasets/temperature-regional.xlsx
+++ b/data.mn/public/datasets/temperature-regional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1664,7 +1664,7 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>25.1</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="57">
@@ -6002,154 +6002,132 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>-2.8</v>
+        <v>-14.7</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.3</v>
+        <v>-8.1</v>
       </c>
       <c r="D254" t="n">
-        <v>-1.8</v>
+        <v>-16.7</v>
       </c>
       <c r="E254" t="n">
-        <v>-6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="F254" t="n">
-        <v>-4.1</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>-14.7</v>
+        <v>-0.6</v>
       </c>
       <c r="C255" t="n">
-        <v>-8.1</v>
+        <v>0.6</v>
       </c>
       <c r="D255" t="n">
-        <v>-16.7</v>
+        <v>-5</v>
       </c>
       <c r="E255" t="n">
-        <v>-16.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F255" t="n">
-        <v>-15.2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>-0.6</v>
+        <v>4.2</v>
       </c>
       <c r="C256" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="D256" t="n">
-        <v>-5</v>
+        <v>5.3</v>
       </c>
       <c r="E256" t="n">
-        <v>-2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F256" t="n">
-        <v>-5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>4.2</v>
+        <v>13.2</v>
       </c>
       <c r="C257" t="n">
-        <v>10.2</v>
+        <v>16</v>
       </c>
       <c r="D257" t="n">
-        <v>5.3</v>
+        <v>13.8</v>
       </c>
       <c r="E257" t="n">
-        <v>8.800000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="F257" t="n">
-        <v>3.7</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>13.2</v>
+        <v>15.4</v>
       </c>
       <c r="C258" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D258" t="n">
-        <v>13.8</v>
+        <v>16.1</v>
       </c>
       <c r="E258" t="n">
-        <v>12.6</v>
+        <v>20.3</v>
       </c>
       <c r="F258" t="n">
-        <v>11.6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>15.4</v>
+        <v>22.4</v>
       </c>
       <c r="C259" t="n">
-        <v>18</v>
+        <v>24.6</v>
       </c>
       <c r="D259" t="n">
-        <v>16.1</v>
+        <v>21.3</v>
       </c>
       <c r="E259" t="n">
-        <v>20.3</v>
+        <v>22.4</v>
       </c>
       <c r="F259" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B260" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="C260" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="D260" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="E260" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="F260" t="n">
         <v>19.3</v>
       </c>
     </row>
@@ -6164,7 +6142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7408,7 +7386,7 @@
         <v>20.6</v>
       </c>
       <c r="D56" t="n">
-        <v>25.1</v>
+        <v>19.3</v>
       </c>
       <c r="E56" t="n">
         <v>19.9</v>
@@ -11752,154 +11730,132 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>-0.3</v>
+        <v>-8.1</v>
       </c>
       <c r="C254" t="n">
-        <v>-1.8</v>
+        <v>-16.7</v>
       </c>
       <c r="D254" t="n">
-        <v>-4.1</v>
+        <v>-15.2</v>
       </c>
       <c r="E254" t="n">
-        <v>-6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="F254" t="n">
-        <v>-2.8</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>-8.1</v>
+        <v>0.6</v>
       </c>
       <c r="C255" t="n">
-        <v>-16.7</v>
+        <v>-5</v>
       </c>
       <c r="D255" t="n">
-        <v>-15.2</v>
+        <v>-5</v>
       </c>
       <c r="E255" t="n">
-        <v>-16.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F255" t="n">
-        <v>-14.7</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="C256" t="n">
-        <v>-5</v>
+        <v>5.3</v>
       </c>
       <c r="D256" t="n">
-        <v>-5</v>
+        <v>3.7</v>
       </c>
       <c r="E256" t="n">
-        <v>-2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>10.2</v>
+        <v>16</v>
       </c>
       <c r="C257" t="n">
-        <v>5.3</v>
+        <v>13.8</v>
       </c>
       <c r="D257" t="n">
-        <v>3.7</v>
+        <v>11.6</v>
       </c>
       <c r="E257" t="n">
-        <v>8.800000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="F257" t="n">
-        <v>4.2</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C258" t="n">
-        <v>13.8</v>
+        <v>16.1</v>
       </c>
       <c r="D258" t="n">
-        <v>11.6</v>
+        <v>13</v>
       </c>
       <c r="E258" t="n">
-        <v>12.6</v>
+        <v>20.3</v>
       </c>
       <c r="F258" t="n">
-        <v>13.2</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>18</v>
+        <v>24.6</v>
       </c>
       <c r="C259" t="n">
-        <v>16.1</v>
+        <v>21.3</v>
       </c>
       <c r="D259" t="n">
-        <v>13</v>
+        <v>19.3</v>
       </c>
       <c r="E259" t="n">
-        <v>20.3</v>
+        <v>22.4</v>
       </c>
       <c r="F259" t="n">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B260" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="C260" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="D260" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="E260" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="F260" t="n">
         <v>22.4</v>
       </c>
     </row>

--- a/data.mn/public/datasets/temperature-regional.xlsx
+++ b/data.mn/public/datasets/temperature-regional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6153,6 +6153,28 @@
         <v>17.6</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="C261" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D261" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E261" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F261" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6164,7 +6186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11903,6 +11925,28 @@
         <v>19.6</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="C261" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D261" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E261" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F261" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
